--- a/PULSE_Optimized_StartStop_TestCases.xlsx
+++ b/PULSE_Optimized_StartStop_TestCases.xlsx
@@ -41,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
-        <bgColor rgb="004472C4"/>
+        <fgColor rgb="002F5496"/>
+        <bgColor rgb="002F5496"/>
       </patternFill>
     </fill>
     <fill>
@@ -446,20 +446,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -538,24 +538,23 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Verify left sidebar navigation menu items display correctly</t>
+          <t>Verify left sidebar displays all main menu items</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on the PULSE dashboard</t>
+          <t>User is logged in to PULSE dashboard</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>1. Observe the left sidebar navigation
-2. Check all menu items are visible
-3. Verify icons are displayed next to each item</t>
+          <t>1. Observe left sidebar
+2. Verify all main menu items are present</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -565,7 +564,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>All navigation items are displayed with correct icons and labels</t>
+          <t>All main menu items displayed with correct icons and labels</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -598,33 +597,33 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Verify AI Operations submenu expands on click</t>
+          <t>Verify AI Operations submenu expands correctly</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on the PULSE dashboard</t>
+          <t>User is on PULSE dashboard</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1. Click on 'AI Operations' in the left sidebar
-2. Observe submenu expansion</t>
+          <t>1. Click on 'AI Operations' in sidebar
+2. Verify submenu items appear</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Submenu items: Maintenance, Alarms, FDD, Smart Cx, Start/Stop</t>
+          <t>Submenu: Maintenance, Alarms, FDD, Smart Cx, Start/Stop</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>AI Operations submenu expands showing all sub-items with proper indentation</t>
+          <t>AI Operations expands showing all submenu items with proper indentation</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -657,44 +656,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Verify Start/Stop page is highlighted when active</t>
+          <t>Verify Start/Stop page loads when clicking menu item</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and AI Operations is expanded</t>
+          <t>User is logged in, AI Operations is expanded</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Click on 'Start/Stop' submenu item
-2. Observe visual state of the menu item</t>
+2. Observe page load</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Start/Stop menu item</t>
+          <t>Start/Stop menu item click</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Start/Stop item is highlighted in purple/active color indicating current page</t>
+          <t>Optimized Start/Stop page loads with all sections visible</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -721,35 +720,34 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Verify Collapse button functionality in sidebar</t>
+          <t>Verify active menu item is highlighted in purple</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>User is on the Start/Stop page with sidebar expanded</t>
+          <t>User is on Start/Stop page</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1. Click the 'Collapse' button at bottom of sidebar
-2. Observe sidebar behavior
-3. Click again to expand</t>
+          <t>1. Observe 'Start/Stop' menu item styling
+2. Compare with other menu items</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Collapse/Expand toggle</t>
+          <t>Start/Stop active state</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Sidebar collapses to show only icons and expands back on toggle</t>
+          <t>Start/Stop item highlighted in purple/active color, distinguishable from other items</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -771,45 +769,45 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Verify Whitespace (DIC) dropdown in header</t>
+          <t>Verify Collapse button functionality</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>User is on the Start/Stop page</t>
+          <t>User is on Start/Stop page with sidebar expanded</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1. Locate the 'Whitespace (DIC)' dropdown in top header
-2. Click on the dropdown
-3. Observe options</t>
+          <t>1. Click 'Collapse' button at bottom of sidebar
+2. Verify sidebar collapses
+3. Click again to expand</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Whitespace (DIC) dropdown</t>
+          <t>Collapse toggle button</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Dropdown opens showing available building/location options</t>
+          <t>Sidebar collapses showing only icons, expands back on second click</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -831,7 +829,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Navigation</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -841,40 +839,39 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Verify search functionality in header</t>
+          <t>Verify sidebar scroll with many menu items</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>User is on the Start/Stop page</t>
+          <t>User is on page with all menu sections expanded</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1. Click on 'Search anything here...' search bar
-2. Type a search term
-3. Observe results</t>
+          <t>1. Expand all sidebar menus
+2. Verify scrolling works within sidebar</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Search term: 'Office 01'</t>
+          <t>All menus expanded</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Search bar accepts input and displays relevant results</t>
+          <t>Sidebar shows scrollbar and allows smooth scrolling without overlapping content</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -896,44 +893,45 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Verify Last Updated timestamp display</t>
+          <t>Verify Whitespace (DIC) dropdown functionality</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>User is on the Start/Stop page</t>
+          <t>User is on Start/Stop page</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1. Observe 'Last Updated: Custom' label in header
-2. Verify timestamp format</t>
+          <t>1. Click 'Whitespace (DIC)' dropdown
+2. Verify options appear
+3. Select a different option</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Last Updated: Custom</t>
+          <t>Whitespace (DIC) dropdown</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Last Updated shows correct timestamp or 'Custom' label with clickable option</t>
+          <t>Dropdown opens showing building/location options, selection updates page data</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -955,34 +953,34 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Verify notification bell icon with badge</t>
+          <t>Verify Search functionality</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>User is on the Start/Stop page</t>
+          <t>User is on Start/Stop page</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1. Locate the notification bell icon in header
-2. Observe badge count
-3. Click on it</t>
+          <t>1. Click 'Search anything here...' field
+2. Type a search term
+3. Verify results</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Notification bell with count badge</t>
+          <t>Search term: 'Office 01'</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Bell icon displays notification count and opens notification panel on click</t>
+          <t>Search accepts input, shows relevant results/suggestions</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1015,33 +1013,33 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Verify user profile icon in header</t>
+          <t>Verify Last Updated: Custom display and time picker</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>User is on the Start/Stop page</t>
+          <t>User is on Start/Stop page</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1. Locate user profile icon in top right
-2. Click on it</t>
+          <t>1. Observe 'Last Updated: Custom' in header
+2. Click on it to verify time picker</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>User profile icon</t>
+          <t>Last Updated timestamp</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Profile icon shows user avatar and opens profile menu/options on click</t>
+          <t>Shows last data refresh time, custom allows time range selection</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1069,50 +1067,50 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Optimized Start/Stop</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Verify page title and description display</t>
+          <t>Verify notification bell icon with badge count</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>User navigates to Start/Stop page</t>
+          <t>User is on Start/Stop page</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1. Observe the page title 'Optimized Start/Stop'
-2. Read the description text
-3. Verify back arrow button</t>
+          <t>1. Locate notification bell in header
+2. Verify badge count visible
+3. Click bell icon</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Title: Optimized Start/Stop, Description about AI-driven pre-conditioning algorithms</t>
+          <t>Bell icon with notification count</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Page title, description, and back navigation arrow are displayed correctly</t>
+          <t>Notification panel opens showing alerts/messages with correct count</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1129,7 +1127,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Optimized Start/Stop</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1139,28 +1137,28 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Verify back arrow navigation</t>
+          <t>Verify user profile icon functionality</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>User is on the Start/Stop page</t>
+          <t>User is logged in</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1. Click the back arrow (←) next to page title
-2. Observe navigation behavior</t>
+          <t>1. Click user profile icon in top-right
+2. Verify profile menu options</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Back arrow button</t>
+          <t>Profile icon click</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>User is navigated to the previous page or parent AI Operations page</t>
+          <t>Profile dropdown shows user info, settings, logout options</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr"/>
@@ -1188,7 +1186,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>AI Control Mode</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1198,34 +1196,34 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Verify all AI Control Mode options are displayed</t>
+          <t>Verify dark/light mode toggle icon</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>User is on the Start/Stop page</t>
+          <t>User is on Start/Stop page</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1. Locate 'AI Control Mode' section
-2. Verify all four mode options are visible</t>
+          <t>1. Click the grid/theme toggle icon in header
+2. Observe theme change</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Modes: Learning, Simulating, Semi-Auto, Autonomous</t>
+          <t>Theme toggle</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>All four AI control mode options are displayed with respective icons</t>
+          <t>Page switches between dark and light themes with all elements properly styled</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1247,49 +1245,50 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>AI Control Mode</t>
+          <t>Page Header</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Verify Semi-Auto mode is currently selected</t>
+          <t>Verify Optimized Start/Stop page title and description</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>User is on the Start/Stop page</t>
+          <t>User navigates to Start/Stop page</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1. Observe the AI Control Mode section
-2. Check which mode is highlighted/selected</t>
+          <t>1. Verify page title 'Optimized Start/Stop'
+2. Read description text
+3. Verify back arrow</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Semi-Auto mode with yellow/orange border highlight</t>
+          <t>Title: Optimized Start/Stop</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Semi-Auto mode is visually highlighted with a distinct border indicating active selection</t>
+          <t>Title displayed correctly with description about AI-driven pre-conditioning algorithms and back arrow navigation</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1306,7 +1305,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>AI Control Mode</t>
+          <t>Page Header</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1316,35 +1315,34 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Verify switching from Semi-Auto to Learning mode</t>
+          <t>Verify back arrow navigation</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page with Semi-Auto selected</t>
+          <t>User is on Start/Stop page</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1. Click on 'Learning' mode option
-2. Observe visual feedback
-3. Verify mode change confirmation</t>
+          <t>1. Click back arrow next to page title
+2. Observe navigation</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Switch from Semi-Auto to Learning</t>
+          <t>Back arrow button</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Mode switches to Learning with appropriate visual indicator and confirmation dialog/toast</t>
+          <t>User navigates to previous page or AI Operations parent page</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1376,7 +1374,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Verify switching to Simulating mode</t>
+          <t>Verify all four AI Control Mode options display</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1386,18 +1384,18 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1. Click on 'Simulating' mode option
-2. Observe behavior change</t>
+          <t>1. Locate 'AI Control Mode' section
+2. Verify all four options visible</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Switch to Simulating mode</t>
+          <t>Modes: Learning, Simulating, Semi-Auto, Autonomous</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Mode switches to Simulating with visual confirmation and schedule data updates accordingly</t>
+          <t>All four mode cards displayed with icons and labels</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1435,7 +1433,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Verify switching to Autonomous mode</t>
+          <t>Verify current mode (Semi-Auto) is highlighted</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1445,18 +1443,18 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1. Click on 'Autonomous' mode option
-2. Observe any warning/confirmation dialogs</t>
+          <t>1. Observe AI Control Mode section
+2. Identify which mode has active/highlighted state</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Switch to Autonomous mode</t>
+          <t>Semi-Auto with yellow/orange border</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>System shows confirmation dialog before switching to Autonomous mode due to full AI control</t>
+          <t>Semi-Auto mode has distinct border/highlight indicating active selection</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1489,33 +1487,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Verify mode switch behavior during active HVAC operation</t>
+          <t>Verify switching to Learning mode</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>HVAC system is actively running optimized schedule</t>
+          <t>Semi-Auto is currently selected</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1. While system is running, attempt to switch modes
-2. Observe system behavior</t>
+          <t>1. Click 'Learning' mode card
+2. Observe visual feedback
+3. Check if confirmation dialog appears</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Mode switch during active operation</t>
+          <t>Click Learning mode</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>System either prevents mode switch with warning or gracefully transitions without disrupting current operations</t>
+          <t>Mode switches to Learning with visual confirmation, schedule may update</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1526,7 +1525,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1548,45 +1547,44 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Verify green checkmark icons on Learning and Simulating modes</t>
+          <t>Verify switching to Simulating mode</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>Semi-Auto is currently selected</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1. Observe Learning mode card
-2. Observe Simulating mode card
-3. Check for green checkmark indicators</t>
+          <t>1. Click 'Simulating' mode card
+2. Observe behavior</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Green checkmark on Learning and Simulating</t>
+          <t>Click Simulating mode</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Green checkmarks indicate these modes have been completed/validated</t>
+          <t>Mode switches to Simulating, system shows simulation data without actual HVAC control</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1603,7 +1601,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Today's Conditions</t>
+          <t>AI Control Mode</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1613,35 +1611,34 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Verify Outdoor Temperature display</t>
+          <t>Verify switching to Autonomous mode with confirmation</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page with weather data available</t>
+          <t>Semi-Auto is currently selected</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1. Locate Today's Conditions section
-2. Verify Outdoor Temp card shows temperature value
-3. Check subtitle text</t>
+          <t>1. Click 'Autonomous' mode card
+2. Verify confirmation/warning dialog</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>27°C, +15 min pre-cool needed</t>
+          <t>Click Autonomous mode</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Outdoor temperature displays correct value in °C with pre-cool adjustment note</t>
+          <t>Confirmation dialog appears before switching to Autonomous (full AI control)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1663,39 +1660,38 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Today's Conditions</t>
+          <t>AI Control Mode</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Verify Relative Humidity display</t>
+          <t>Verify mode switch during active HVAC operation</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page with weather data available</t>
+          <t>System is actively running an optimized schedule</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1. Locate Relative Humidity card
-2. Verify percentage value
-3. Check subtitle</t>
+          <t>1. While HVAC is running, attempt to switch mode
+2. Observe system behavior</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>50%, Higher latent load</t>
+          <t>Mode switch during operation</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Relative Humidity shows correct percentage with load indicator</t>
+          <t>System either prevents switch with warning or gracefully transitions</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1706,7 +1702,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1723,50 +1719,49 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Today's Conditions</t>
+          <t>AI Control Mode</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Edge Case</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Verify Forecast Peak display</t>
+          <t>Verify rapid mode switching behavior</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page with weather data available</t>
+          <t>User is on Start/Stop page</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1. Locate Forecast Peak card
-2. Verify temperature value
-3. Check subtitle</t>
+          <t>1. Rapidly click between different modes
+2. Observe final state</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>38°C, Extended run likely</t>
+          <t>Quick successive clicks on all modes</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Forecast Peak shows predicted peak temperature with operational impact note</t>
+          <t>System handles gracefully, settles on last valid selection without errors</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Edge Case</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -1783,17 +1778,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Today's Conditions</t>
+          <t>AI Control Mode</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Verify Temperature Compliance display</t>
+          <t>Verify green checkmarks on Learning and Simulating modes</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1803,30 +1798,29 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1. Locate Temperature Compliance card
-2. Verify percentage value
-3. Check color indicator and subtitle</t>
+          <t>1. Observe checkmark icons on Learning and Simulating cards
+2. Verify meaning</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8%, Normal weekday</t>
+          <t>Green checkmarks on mode cards</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Temperature Compliance shows percentage with green indicator for normal conditions</t>
+          <t>Green checkmarks indicate these phases have been completed/validated</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -1843,50 +1837,49 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Today's Conditions</t>
+          <t>AI Control Mode</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Verify No of Rooms display</t>
+          <t>Verify role-based access to mode switching</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User with read-only role logged in</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1. Locate 'No of Rooms' card
-2. Verify room count
-3. Check subtitle</t>
+          <t>1. Login as read-only user
+2. Attempt to switch AI Control Mode</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>12, Building retained heat</t>
+          <t>Read-only user credentials</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Number of rooms displays correctly with status description</t>
+          <t>Mode switching disabled/greyed out for unauthorized users</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -1908,44 +1901,44 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Verify color coding of condition cards</t>
+          <t>Verify Outdoor Temperature display (27°C)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User is on Start/Stop page, weather data available</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1. Observe color indicators on each condition card
-2. Green for normal, yellow/orange for warnings</t>
+          <t>1. Locate 'Outdoor Temp (7 AM)' card
+2. Verify temperature value and subtitle</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Color coding: Green (normal), Yellow (caution), Orange (warning)</t>
+          <t>27°C, +15 min pre-cool needed</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Each condition card has appropriate color coding based on severity/status</t>
+          <t>Shows correct outdoor temperature with pre-cool impact note</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -1967,34 +1960,33 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Verify display when weather data is unavailable</t>
+          <t>Verify Relative Humidity display (50%)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Weather service/API is down or unreachable</t>
+          <t>User is on Start/Stop page</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1. Simulate weather data unavailability
-2. Navigate to Start/Stop page
-3. Observe Today's Conditions section</t>
+          <t>1. Locate 'Relative Humidity' card
+2. Verify percentage and subtitle</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>No weather data available</t>
+          <t>50%, Higher latent load</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Section shows appropriate error message or 'Data unavailable' placeholder, not blank or broken UI</t>
+          <t>Shows humidity percentage with latent load indication</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -2005,7 +1997,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2027,44 +2019,44 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Edge Case</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Verify display with extreme temperature values</t>
+          <t>Verify Forecast Peak display (38°C)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>System receives extreme weather data</t>
+          <t>User is on Start/Stop page</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1. Input extreme temperature data (e.g., -40°C or 55°C)
-2. Observe how the UI handles display</t>
+          <t>1. Locate 'Forecast Peak' card
+2. Verify temperature and subtitle</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Temperature: -40°C or 55°C</t>
+          <t>38°C, Extended run likely</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>UI properly displays extreme values without layout breaking or data overflow</t>
+          <t>Shows peak forecast temperature with operational impact note</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Edge Case</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -2081,7 +2073,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Optimized Schedule</t>
+          <t>Today's Conditions</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2091,7 +2083,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Verify schedule section title and description</t>
+          <t>Verify Temperature Compliance display (8%)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2101,29 +2093,29 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1. Locate 'Today's Optimized Schedule' section
-2. Read the subtitle description</t>
+          <t>1. Locate 'Temperature Compliance' card
+2. Verify percentage and subtitle</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Title: Today's Optimized Schedule</t>
+          <t>8%, Normal weekday</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Section displays title with description about AI-calculated start/stop times adjusted for conditions</t>
+          <t>Shows compliance percentage with day-type context</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -2140,7 +2132,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Optimized Schedule</t>
+          <t>Today's Conditions</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2150,28 +2142,28 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Verify Melvin's Office zone card data</t>
+          <t>Verify No of Rooms display (12)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page with schedule data loaded</t>
+          <t>User is on Start/Stop page</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1. Locate 'Melvin's Office' card
-2. Verify all fields are populated</t>
+          <t>1. Locate 'No of Rooms' card
+2. Verify room count and subtitle</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Occupancy Start: 07:00 AM, Optimized Start: 06:05 AM, Pre-cool Duration: 55 min, Occupancy End: 06:00 PM, Optimized Stop: 05:40 PM, Coast Duration: 20 min saved, Energy Saved: 0.4 kWh</t>
+          <t>12, Building retained heat</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>All schedule parameters display correct values with proper formatting</t>
+          <t>Shows total rooms being managed with heat retention note</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -2199,49 +2191,49 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Optimized Schedule</t>
+          <t>Today's Conditions</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Verify Optimized Start time is before Occupancy Start</t>
+          <t>Verify color coding of condition cards</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page with schedule loaded</t>
+          <t>User is on Start/Stop page</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1. For each zone card, compare Occupancy Start and Optimized Start times
-2. Verify Optimized Start is always earlier</t>
+          <t>1. Observe color gradient on each condition card
+2. Verify color severity mapping</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Multiple zone cards</t>
+          <t>Green (normal), Yellow (moderate), Orange (high), Purple (info)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Optimized Start time is always earlier than Occupancy Start time (pre-cooling starts before occupancy)</t>
+          <t>Each card has appropriate color coding matching the severity/nature of the value</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -2258,38 +2250,39 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Optimized Schedule</t>
+          <t>Today's Conditions</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Verify Optimized Stop time is before Occupancy End</t>
+          <t>Verify display when weather service is unavailable</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page with schedule loaded</t>
+          <t>Weather API/service is down</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1. For each zone card, compare Occupancy End and Optimized Stop times
-2. Verify Optimized Stop is earlier (coast period)</t>
+          <t>1. Simulate weather service failure
+2. Navigate to Start/Stop page
+3. Observe conditions section</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Multiple zone cards</t>
+          <t>Weather API timeout/error</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Optimized Stop time is always earlier than Occupancy End (allowing coast-through period)</t>
+          <t>Shows 'Data unavailable' or cached values with timestamp, not blank/broken</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2300,7 +2293,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -2317,49 +2310,49 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Optimized Schedule</t>
+          <t>Today's Conditions</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Edge Case</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Verify Pre-cool Duration calculation accuracy</t>
+          <t>Verify display with extreme temperature values</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>Weather reports extreme temperatures</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1. Calculate difference between Occupancy Start and Optimized Start
-2. Compare with displayed Pre-cool Duration</t>
+          <t>1. System receives extreme temp data (-40°C or 55°C)
+2. Observe card display</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Melvin's Office: 07:00 AM - 06:05 AM = 55 min</t>
+          <t>Temperature: -40°C or 55°C</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Pre-cool Duration matches the time difference between Occupancy Start and Optimized Start</t>
+          <t>UI displays extreme values correctly without layout breaking</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Edge Case</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -2376,7 +2369,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Optimized Schedule</t>
+          <t>Today's Conditions</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2386,28 +2379,28 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Verify Coast Duration calculation accuracy</t>
+          <t>Verify conditions update when building changes</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User changes building selection</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1. Calculate difference between Occupancy End and Optimized Stop
-2. Compare with displayed Coast Duration</t>
+          <t>1. Change building in dropdown
+2. Observe Today's Conditions update</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Melvin's Office: 06:00 PM - 05:40 PM = 20 min</t>
+          <t>Different building selection</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Coast Duration matches the time difference between Occupancy End and Optimized Stop</t>
+          <t>All condition cards refresh with new building's data</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2440,44 +2433,44 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Verify Energy Saved Today values are positive</t>
+          <t>Verify schedule section header and description</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page with schedule loaded</t>
+          <t>User is on Start/Stop page</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1. Check Energy Saved Today value for each zone
-2. Verify all values are positive or zero</t>
+          <t>1. Locate 'Today's Optimized Schedule' section
+2. Read subtitle</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Energy values: 0.4 kWh, 0.4 kWh, 1.9 kWh, etc.</t>
+          <t>Section header and description</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>All Energy Saved values are non-negative numbers displayed in kWh</t>
+          <t>Shows title with description about AI-calculated times adjusted for conditions</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -2504,28 +2497,28 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Verify zone running status indicator</t>
+          <t>Verify Melvin's Office zone card - all fields</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page with active zones</t>
+          <t>Schedule data is loaded</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1. Observe status indicators at bottom of each zone card
-2. Check for 'Running — At setpoint' or 'Idle' status</t>
+          <t>1. Locate Melvin's Office card
+2. Verify all field values</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Status: Running — At setpoint, Idle</t>
+          <t>Occupancy Start: 07:00 AM, Optimized Start: 06:05 AM, Pre-cool: 55 min, End: 06:00 PM, Stop: 05:40 PM, Coast: 20 min saved, Energy: 0.4 kWh</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Each zone displays correct running status with appropriate color (green for running, grey for idle)</t>
+          <t>All values displayed correctly with proper formatting and color coding</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2563,28 +2556,28 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Verify all 12 zone cards are displayed</t>
+          <t>Verify Mezzanine Office Space 1 zone card</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page (12 rooms indicated in conditions)</t>
+          <t>Schedule data is loaded</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1. Count all zone cards in the schedule section
-2. Verify count matches 'No of Rooms' value</t>
+          <t>1. Locate Mezzanine Office Space 1 card
+2. Verify all values</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Expected zones: Melvin's Office, Mezzanine Office Space 1, 2, 3, Mezzanine Pantry, White Space 01, 02, 03, Office 01, 02, Electrical Room, White_Space-Corridor</t>
+          <t>Occupancy Start: 07:00 AM, Optimized Start: 06:18 AM, Pre-cool: 45 min, End: 06:00 PM, Stop: 06:35 PM, Coast: 15 min, Energy: 0.4 kWh</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>All 12 zone cards are displayed matching the room count in Today's Conditions</t>
+          <t>All values correct, Running - At setpoint status shown in green</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2617,44 +2610,44 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Verify time values are color-coded (green for optimized)</t>
+          <t>Verify Mezzanine Office Space 3 zone card</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>Schedule data is loaded</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1. Observe Optimized Start and Optimized Stop time values
-2. Verify they appear in green color</t>
+          <t>1. Locate Mezzanine Office Space 3 card
+2. Verify all values</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Green colored time values</t>
+          <t>Occupancy Start: 07:00 AM, Optimized Start: 06:05 AM, Pre-cool: 55 min, End: 06:00 PM, Stop: 06:30 PM, Coast: 30 min, Energy: 0.2 kWh</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Optimized Start and Optimized Stop times are displayed in green to differentiate from standard times</t>
+          <t>All values correct with Running status</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -2681,34 +2674,34 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Verify White_Space-Corridor shows no data (dashes)</t>
+          <t>Verify Mezzanine Office Space 2 zone card with Idle status</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>Schedule data is loaded</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1. Locate White_Space-Corridor card
-2. Observe all field values show dashes (-)</t>
+          <t>1. Locate Mezzanine Office Space 2 card
+2. Verify all values and Idle status</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>All fields showing '-' for White_Space-Corridor</t>
+          <t>Occupancy Start: 07:00 AM, Optimized Start: 06:10 AM, Pre-cool: 50 min, End: 06:00 PM, Stop: 05:35 PM, Coast: 25 min, Energy: 1.9 kWh, Status: Idle</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Zone displays dashes for all parameters indicating no schedule/unoccupied zone</t>
+          <t>All values correct, Status shows 'Idle' in yellow/orange</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2735,44 +2728,44 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Edge Case</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Verify schedule display when occupancy start equals optimized start</t>
+          <t>Verify Mezzanine Pantry zone card</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Zone where pre-cool is not needed (e.g., mild weather)</t>
+          <t>Schedule data is loaded</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1. Check if any zone has matching Occupancy Start and Optimized Start
-2. Verify Pre-cool Duration shows 0 min</t>
+          <t>1. Locate Mezzanine Pantry card
+2. Verify all values</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Pre-cool Duration: 0 min</t>
+          <t>Occupancy Start: 08:00 AM, Optimized Start: 06:42 AM, Pre-cool: 78 min, End: 06:00 PM, Stop: 06:22 PM, Coast: 38 min, Energy: 0.7 kWh</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>When no pre-cooling needed, Pre-cool Duration shows 0 and times match</t>
+          <t>All values correct, Running - At setpoint</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Edge Case</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -2794,34 +2787,33 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Verify behavior when schedule data fails to load</t>
+          <t>Verify White Space 01 zone card</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Network error or API failure for schedule data</t>
+          <t>Schedule data is loaded</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1. Simulate API failure for schedule data
-2. Navigate to Start/Stop page
-3. Observe schedule section</t>
+          <t>1. Locate White Space 01 card
+2. Verify all values</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>API timeout/error</t>
+          <t>Occupancy Start: 07:00 AM, Optimized Start: 06:15 AM, Pre-cool: 48 min, End: 06:00 PM, Stop: 06:22 PM, Coast: 38 min, Energy: 0.4 kWh</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Section shows loading error message with retry option, not blank cards</t>
+          <t>All values correct, Running - At setpoint</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2832,7 +2824,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -2854,44 +2846,44 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Edge Case</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Verify schedule with overnight occupancy</t>
+          <t>Verify White Space 02 zone card</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Zone has occupancy spanning midnight (e.g., 10 PM to 6 AM)</t>
+          <t>Schedule data is loaded</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>1. Configure a zone with overnight occupancy
-2. Observe how schedule handles day boundary</t>
+          <t>1. Locate White Space 02 card
+2. Verify all values</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Occupancy Start: 10:00 PM, Occupancy End: 06:00 AM (next day)</t>
+          <t>Occupancy Start: 07:00 AM, Optimized Start: 06:10 AM, Pre-cool: 50 min, End: 06:00 PM, Stop: 05:35 PM, Coast: 25 min, Energy: 0.4 kWh</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Schedule correctly handles overnight occupancy without calculation errors</t>
+          <t>All values correct, Running - At setpoint</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Edge Case</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -2918,34 +2910,34 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Verify Mezzanine Office Space 2 shows Idle status</t>
+          <t>Verify Office 01 zone card</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>Schedule data is loaded</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1. Locate Mezzanine Office Space 2 card
-2. Check the status indicator</t>
+          <t>1. Locate Office 01 card
+2. Verify all values</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Status: Idle (shown in yellow/orange)</t>
+          <t>Occupancy Start: 07:00 AM, Optimized Start: 06:10 AM, Pre-cool: 48 min, End: 06:00 PM, Stop: 06:40 PM, Coast: 22 min, Energy: 0.2 kWh</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Zone correctly shows 'Idle' status when not actively running</t>
+          <t>All values correct, Running - At setpoint</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2967,7 +2959,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Algorithm Intelligence</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2977,29 +2969,28 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Verify Thermal Mass Learning section display</t>
+          <t>Verify White Space 03 zone card</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>User scrolls to Algorithm Intelligence section</t>
+          <t>Schedule data is loaded</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1. Locate 'Thermal Mass Learning' card
-2. Verify description and parameters
-3. Check expandable fields</t>
+          <t>1. Locate White Space 03 card
+2. Verify all values</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Fields: Model Accuracy, Training Data, Re-training Cycle</t>
+          <t>Occupancy Start: 07:00 AM, Optimized Start: 06:55 AM, Pre-cool: 65 min, End: 06:00 PM, Stop: 05:40 PM, Coast: 20 min, Energy: 0.3 kWh</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Thermal Mass Learning card shows description about ML model and expandable parameter fields</t>
+          <t>All values correct, Running - At setpoint</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -3027,7 +3018,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Algorithm Intelligence</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3037,28 +3028,28 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Verify Weather Forecast Integration section</t>
+          <t>Verify Office 02 zone card</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>User scrolls to Algorithm Intelligence section</t>
+          <t>Schedule data is loaded</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1. Locate 'Weather Forecast Integration' card
-2. Verify description and parameters</t>
+          <t>1. Locate Office 02 card
+2. Verify all values</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Fields: Forecast Source, Update Frequency, Accuracy (24h)</t>
+          <t>Occupancy Start: 08:00 AM, Optimized Start: 06:42 AM, Pre-cool: 78 min, End: 06:00 PM, Stop: 05:22 PM, Coast: 38 min, Energy: 0.3 kWh</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Weather Forecast card shows integration details with expandable parameters</t>
+          <t>All values correct, Running - At setpoint</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -3086,7 +3077,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Algorithm Intelligence</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3096,28 +3087,28 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Verify Occupancy Prediction section</t>
+          <t>Verify Electrical Room zone card</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>User scrolls to Algorithm Intelligence section</t>
+          <t>Schedule data is loaded</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1. Locate 'Occupancy Prediction' card
-2. Verify description and parameters</t>
+          <t>1. Locate Electrical Room card
+2. Verify all values</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Fields: Prediction Accuracy, Low Occupancy Savings, Holiday Detection</t>
+          <t>Occupancy Start: 07:00 AM, Optimized Start: 06:18 AM, Pre-cool: 45 min, End: 06:00 PM, Stop: 05:40 PM, Coast: 20 min, Energy: 0.2 kWh</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Occupancy Prediction card shows access card/calendar integration details</t>
+          <t>All values correct, Running - At setpoint</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -3145,7 +3136,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Algorithm Intelligence</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3155,34 +3146,34 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Verify Coast-Through Calculation section</t>
+          <t>Verify White_Space-Corridor zone card shows no data</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>User scrolls to Algorithm Intelligence section</t>
+          <t>Schedule data is loaded</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1. Locate 'Coast-Through Calculation' card
-2. Verify description and parameters</t>
+          <t>1. Locate White_Space-Corridor card
+2. Verify all fields show dashes (-)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Fields: Avg Coast Time, Max Temp Rise Allowed, Comfort Compliance</t>
+          <t>All fields: '-'</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Coast-Through card explains early HVAC stop methodology with parameters</t>
+          <t>Zone displays dashes indicating no schedule/unoccupied</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3204,7 +3195,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Algorithm Intelligence</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3214,28 +3205,28 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Verify Cooling Model Parameters section</t>
+          <t>Verify all 12 zone cards are displayed</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>User scrolls to Algorithm Intelligence section</t>
+          <t>User is on Start/Stop page</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1. Locate 'Cooling Model Parameters' card
-2. Verify all parameters listed</t>
+          <t>1. Count all zone cards
+2. Compare with 'No of Rooms' (12)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Fields: Building Time Constant (τ), Envelope U-Value, Internal Heat Gain, Solar Heat Gain Coefficient, Cooling Capacity, Pull-Down Rate</t>
+          <t>12 rooms expected</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>All cooling model parameters are displayed with expand/collapse arrows</t>
+          <t>Exactly 12 zone cards displayed matching room count</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -3263,7 +3254,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Algorithm Intelligence</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3273,34 +3264,34 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Verify Weekly Performance Summary section</t>
+          <t>Verify Optimized Start is always before Occupancy Start</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>User scrolls to Algorithm Intelligence section</t>
+          <t>Schedule loaded for all zones</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1. Locate 'Weekly Performance Summary' card
-2. Verify metrics displayed</t>
+          <t>1. For each zone, compare Optimized Start with Occupancy Start
+2. Verify pre-cooling logic</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Fields: Total Energy Saved (1,840 kWh), Cost Savings, Comfort Violations, Avg Start Advance, Avg Coast Duration, Model Recalibrations</t>
+          <t>All zones comparison</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Weekly Performance shows summary with Total Energy Saved value of 1,840 kWh highlighted in green</t>
+          <t>Optimized Start is always earlier than Occupancy Start</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3322,7 +3313,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Algorithm Intelligence</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3332,35 +3323,34 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Verify expandable/collapsible parameter fields</t>
+          <t>Verify Pre-cool Duration = Occupancy Start - Optimized Start</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>User is viewing Algorithm Intelligence section</t>
+          <t>Schedule data loaded</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1. Click on any parameter field with expand arrow (&gt;)
-2. Observe expansion behavior
-3. Click again to collapse</t>
+          <t>1. Melvin's Office: 07:00 AM - 06:05 AM = 55 min
+2. Verify displayed Pre-cool matches</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Click on 'Model Accuracy' expand arrow</t>
+          <t>07:00 - 06:05 = 55 min</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Parameter field expands to show detailed value/graph and collapses on second click</t>
+          <t>Pre-cool Duration matches time difference calculation</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -3382,48 +3372,49 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Algorithm Intelligence</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Verify section description text</t>
+          <t>Verify Coast Duration = Occupancy End - Optimized Stop</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>User scrolls to Algorithm Intelligence section</t>
+          <t>Schedule data loaded</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>1. Read the section subtitle/description</t>
+          <t>1. Melvin's Office: 06:00 PM - 05:40 PM = 20 min
+2. Verify displayed Coast Duration</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Description about AI calculating optimal start/stop times</t>
+          <t>18:00 - 17:40 = 20 min</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Description clearly explains that AI learns from building physics, occupancy patterns, and weather data</t>
+          <t>Coast Duration matches time difference calculation</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -3440,7 +3431,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Annual Impact</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3450,28 +3441,28 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Verify Annual Savings card display</t>
+          <t>Verify Running - At setpoint status indicator (green)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>User scrolls to Annual Impact section</t>
+          <t>Zone is actively running</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>1. Locate 'Annual Savings' card
-2. Verify icon, value, and subtitle</t>
+          <t>1. Locate zones with green status
+2. Verify text and color</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Annual Savings - Reduced HVAC runtime hours</t>
+          <t>Status: Running - At setpoint (green)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Annual Savings card displays with learning icon, value, and 'Reduced HVAC runtime hours' subtitle</t>
+          <t>Green indicator with 'Running - At setpoint' text at bottom of card</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3499,7 +3490,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Annual Impact</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3509,28 +3500,28 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Verify Energy Reduced card display</t>
+          <t>Verify Idle status indicator (yellow/orange)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>User scrolls to Annual Impact section</t>
+          <t>Zone is not running</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1. Locate 'Energy Reduced' card
-2. Verify icon, value, and subtitle</t>
+          <t>1. Locate Mezzanine Office Space 2
+2. Verify 'Idle' status</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Energy Reduced - 25% less from fixed schedule</t>
+          <t>Status: Idle (yellow)</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Energy Reduced card shows percentage reduction compared to fixed schedule</t>
+          <t>Yellow indicator with 'Idle' text at bottom of card</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3558,49 +3549,49 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Annual Impact</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Verify Emissions Avoided card display</t>
+          <t>Verify green color for Optimized Start/Stop values</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>User scrolls to Annual Impact section</t>
+          <t>Schedule data loaded</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1. Locate 'Emissions Avoided' card
-2. Verify icon, value, and subtitle</t>
+          <t>1. Observe Optimized Start and Stop time values
+2. Verify green color</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Emissions Avoided - Equivalent to 18 cars/year</t>
+          <t>Green colored time values</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Emissions Avoided card displays with equivalent car emissions comparison</t>
+          <t>Optimized times displayed in green to differentiate from standard times</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -3617,49 +3608,49 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Annual Impact</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Verify Equipment Life Extended card display</t>
+          <t>Verify card layout - 3 cards per row on desktop</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>User scrolls to Annual Impact section</t>
+          <t>Desktop resolution (1920x1080)</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1. Locate 'Equipment Life Extended' card
-2. Verify icon, value, and subtitle</t>
+          <t>1. Observe zone card grid layout
+2. Verify 3 cards per row</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Equipment Life Extended - Fewer start/stop cycles</t>
+          <t>Desktop resolution</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Equipment Life card shows extension benefit with fewer start/stop cycles explanation</t>
+          <t>3 zone cards per row with equal spacing and consistent sizing</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -3676,49 +3667,49 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Annual Impact</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Verify Annual Impact section visual design</t>
+          <t>Verify Energy Saved Today values are positive</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>User scrolls to Annual Impact section</t>
+          <t>Schedule data loaded</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1. Observe the gradient colored cards
-2. Verify consistent card sizing and alignment</t>
+          <t>1. Check Energy Saved for each zone
+2. Verify all &gt;= 0</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Purple/green gradient cards with icons</t>
+          <t>0.4, 0.4, 0.2, 1.9, 0.7, 0.4, 0.4, 0.2, 0.3, 0.3, 0.2 kWh</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>All four impact cards have consistent gradient styling, proper spacing, and aligned content</t>
+          <t>All Energy Saved values non-negative with kWh unit</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -3735,49 +3726,49 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Edge Case</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Verify footer version and copyright information</t>
+          <t>Verify Optimized Stop exceeds Occupancy End (anomaly check)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>User scrolls to bottom of page</t>
+          <t>Zones with Stop &gt; End</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1. Observe footer content
-2. Verify version number and copyright</t>
+          <t>1. Check Mezz Office Space 1: Stop 06:35 PM &gt; End 06:00 PM
+2. Flag if this is bug</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>v1.0.0 - Test | @2026. All Right Reserved.</t>
+          <t>Stop 06:35 PM &gt; End 06:00 PM</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Footer displays correct version number and copyright year</t>
+          <t>Optimized Stop should NOT exceed Occupancy End (coast-through violated)</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Edge Case</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -3794,49 +3785,50 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Verify Terms of Use link</t>
+          <t>Verify behavior when schedule API fails</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>User is at the bottom of the page</t>
+          <t>API error for schedule data</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Terms of Use' link in footer
-2. Observe navigation</t>
+          <t>1. Simulate schedule API failure
+2. Navigate to page
+3. Observe</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Terms of Use link</t>
+          <t>API timeout/error</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Link navigates to Terms of Use page or opens in new tab</t>
+          <t>Error message with retry option, not blank cards</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -3853,49 +3845,49 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Edge Case</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Verify Policy link</t>
+          <t>Verify schedule with overnight occupancy</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>User is at the bottom of the page</t>
+          <t>Zone has 10 PM - 6 AM schedule</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Policy' link in footer
-2. Observe navigation</t>
+          <t>1. Configure overnight occupancy
+2. Observe schedule handling</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Policy link</t>
+          <t>Occupancy: 10:00 PM to 06:00 AM</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Link navigates to Privacy Policy page or opens in new tab</t>
+          <t>System correctly handles midnight boundary crossing</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Edge Case</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -3912,7 +3904,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3922,34 +3914,34 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Verify Support link</t>
+          <t>Verify time format consistency (12-hour AM/PM)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>User is at the bottom of the page</t>
+          <t>Schedule data loaded</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>1. Click 'Support' link in footer
-2. Observe navigation</t>
+          <t>1. Check all time values
+2. Verify 12-hour format</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Support link</t>
+          <t>Format: HH:MM AM/PM</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Link navigates to Support/Help page or opens support chat</t>
+          <t>All times use consistent 12-hour format with AM/PM</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3971,7 +3963,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3981,34 +3973,34 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Verify chat widget (Intercom-style) button</t>
+          <t>Verify schedule updates when building changes</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>User is on the Start/Stop page</t>
+          <t>User changes building</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1. Locate the orange/yellow chat bubble in bottom-right corner
-2. Click on it</t>
+          <t>1. Select different building
+2. Observe schedule update</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Chat widget button</t>
+          <t>New building selection</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Chat widget opens allowing user to send messages to support team</t>
+          <t>Zone cards refresh with new building's data</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4030,49 +4022,50 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Verify authentication required to access Start/Stop page</t>
+          <t>Verify Energy Saved accumulates throughout the day</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>User is not logged in</t>
+          <t>System operational during day</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>1. Attempt to access Start/Stop page URL directly without authentication
-2. Observe behavior</t>
+          <t>1. Check Energy Saved AM
+2. Check again PM
+3. Compare</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Direct URL access without login session</t>
+          <t>Morning vs afternoon values</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>User is redirected to login page; unauthorized access is denied</t>
+          <t>Energy Saved increases as optimization runs during day</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -4089,50 +4082,49 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Algorithm Intelligence</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Verify role-based access to AI Control Mode switching</t>
+          <t>Verify section title and description text</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>User with read-only role is logged in</t>
+          <t>User scrolls to Algorithm Intelligence</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>1. Login as read-only user
-2. Attempt to switch AI Control Mode
-3. Observe response</t>
+          <t>1. Locate section
+2. Verify title and description</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Read-only user credentials</t>
+          <t>Title: Algorithm Intelligence</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Read-only users cannot switch AI Control modes; action is disabled or shows permission error</t>
+          <t>Shows title with AI learning description</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -4149,50 +4141,49 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Algorithm Intelligence</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Verify API endpoint security for schedule data</t>
+          <t>Verify Thermal Mass Learning card and fields</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>User has access to browser developer tools</t>
+          <t>User in Algorithm Intelligence section</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>1. Open browser dev tools
-2. Inspect network requests for schedule data
-3. Verify API uses authentication tokens</t>
+          <t>1. Locate card
+2. Verify description and fields</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Network request inspection</t>
+          <t>Fields: Model Accuracy, Training Data, Re-training Cycle</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>All API calls include proper authentication headers; no sensitive data in URL parameters</t>
+          <t>Card shows ML description with expandable fields</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -4209,50 +4200,49 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Algorithm Intelligence</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Verify XSS protection in search field</t>
+          <t>Verify Weather Forecast Integration card</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User in Algorithm Intelligence section</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>1. Enter script tag in search field: &lt;script&gt;alert('XSS')&lt;/script&gt;
-2. Submit search
-3. Observe behavior</t>
+          <t>1. Locate card
+2. Verify fields</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Input: &lt;script&gt;alert('XSS')&lt;/script&gt;</t>
+          <t>Fields: Forecast Source, Update Frequency, Accuracy (24h)</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Input is sanitized; no script execution occurs; search shows no results safely</t>
+          <t>Shows weather integration with expandable parameters</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -4269,39 +4259,38 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Algorithm Intelligence</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Verify session timeout on Start/Stop page</t>
+          <t>Verify Occupancy Prediction card</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and idle for extended period</t>
+          <t>User in Algorithm Intelligence section</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>1. Login and navigate to Start/Stop page
-2. Wait for session timeout period
-3. Attempt to interact with page</t>
+          <t>1. Locate card
+2. Verify fields</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Session timeout: 30 minutes idle</t>
+          <t>Fields: Prediction Accuracy, Low Occupancy Savings, Holiday Detection</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Session expires after timeout; user is prompted to re-login; no stale data displayed</t>
+          <t>Shows prediction methodology with expandable fields</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -4312,7 +4301,7 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -4329,50 +4318,49 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Algorithm Intelligence</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Verify HTTPS enforcement for all page resources</t>
+          <t>Verify Coast-Through Calculation card</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>User accesses the Start/Stop page</t>
+          <t>User in Algorithm Intelligence section</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>1. Open browser dev tools &gt; Security tab
-2. Verify all resources load over HTTPS
-3. Check for mixed content warnings</t>
+          <t>1. Locate card
+2. Verify fields</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>All page resources (CSS, JS, API calls, images)</t>
+          <t>Fields: Avg Coast Time, Max Temp Rise Allowed, Comfort Compliance</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>All resources are served over HTTPS; no mixed content warnings</t>
+          <t>Shows coast-through methodology with parameters</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -4389,39 +4377,38 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Algorithm Intelligence</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Verify no sensitive data exposed in browser console</t>
+          <t>Verify Cooling Model Parameters card (6 fields)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User in Algorithm Intelligence section</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>1. Open browser developer console
-2. Check for any logged sensitive information
-3. Review console output</t>
+          <t>1. Locate card
+2. Verify all 6 parameters</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Console log inspection</t>
+          <t>Building Time Constant, Envelope U-Value, Internal Heat Gain, Solar Heat Gain Coeff, Cooling Capacity, Pull-Down Rate</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>No API keys, tokens, passwords, or sensitive building data is logged to console</t>
+          <t>All 6 parameters listed with expand arrows</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -4432,7 +4419,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -4449,50 +4436,49 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Algorithm Intelligence</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Verify unauthorized mode change via API manipulation</t>
+          <t>Verify Weekly Performance Summary - Total Energy Saved</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>User has access to browser dev tools</t>
+          <t>User in Algorithm Intelligence section</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>1. Capture the API call for mode switch
-2. Replay with modified parameters or different user token
-3. Observe server response</t>
+          <t>1. Locate Weekly Performance
+2. Verify 1,840 kWh in green</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Modified API request with invalid/expired token</t>
+          <t>Total Energy Saved: 1,840 kWh (green), Cost Savings, Comfort Violations, Avg Start Advance, Avg Coast Duration, Model Recalibrations</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Server rejects unauthorized requests with 401/403 status code</t>
+          <t>Total Energy Saved highlighted in green with correct value</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -4509,50 +4495,50 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Algorithm Intelligence</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Verify page load time for Start/Stop page</t>
+          <t>Verify expandable fields click functionality</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>User has stable internet connection</t>
+          <t>User in Algorithm Intelligence section</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Start/Stop page
-2. Measure total page load time including all zone cards
-3. Check for loading indicators</t>
+          <t>1. Click expand arrow on any parameter
+2. Observe expansion
+3. Click to collapse</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Expected load time: &lt; 3 seconds</t>
+          <t>Click Model Accuracy expand arrow</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Page loads completely within 3 seconds with all zone data populated</t>
+          <t>Field expands showing value, collapses on second click</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
@@ -4569,50 +4555,49 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Algorithm Intelligence</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Verify real-time data refresh for zone status</t>
+          <t>Verify display when model not yet trained</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page with running zones</t>
+          <t>New building with no data</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>1. Observe zone status updates
-2. Verify if data refreshes automatically
-3. Check refresh interval</t>
+          <t>1. Select new building
+2. Observe section</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Auto-refresh interval</t>
+          <t>New building, no training data</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Zone status updates in real-time or at regular intervals without full page reload</t>
+          <t>Shows 'Training in progress' or 'Insufficient data'</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -4629,50 +4614,49 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Responsiveness</t>
+          <t>Annual Impact</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Verify page layout on tablet device (iPad)</t>
+          <t>Verify Annual Savings card display</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>User accesses page on tablet device</t>
+          <t>User scrolls to Annual Impact</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>1. Open Start/Stop page on tablet (1024x768)
-2. Verify zone cards layout
-3. Check all sections are accessible</t>
+          <t>1. Locate 'Annual Savings' card
+2. Verify icon, value, subtitle</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Tablet resolution: 1024x768</t>
+          <t>Annual Savings - Reduced HVAC runtime hours</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Page adapts to tablet layout; zone cards may show 2 per row; all content accessible</t>
+          <t>Shows savings value with correct icon and subtitle</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
@@ -4689,50 +4673,49 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Responsiveness</t>
+          <t>Annual Impact</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Verify page layout on mobile device</t>
+          <t>Verify Energy Reduced card (25% less)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>User accesses page on mobile device</t>
+          <t>User scrolls to Annual Impact</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>1. Open Start/Stop page on mobile (375x812)
-2. Verify scrolling and card stacking
-3. Check navigation accessibility</t>
+          <t>1. Locate 'Energy Reduced' card
+2. Verify percentage</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Mobile resolution: 375x812</t>
+          <t>Energy Reduced - 25% less from fixed schedule</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Page is responsive; cards stack vertically; sidebar becomes hamburger menu; all data readable</t>
+          <t>Shows reduction percentage compared to fixed schedule</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -4749,50 +4732,49 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Responsiveness</t>
+          <t>Annual Impact</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Verify page layout on large monitor (1920x1080)</t>
+          <t>Verify Emissions Avoided card</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>User accesses page on large monitor</t>
+          <t>User scrolls to Annual Impact</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>1. Open Start/Stop page on full HD monitor
-2. Verify zone cards show 3 per row
-3. Check spacing and alignment</t>
+          <t>1. Locate 'Emissions Avoided' card
+2. Verify value</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Desktop resolution: 1920x1080</t>
+          <t>Emissions Avoided - Equivalent to 18 cars/year</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Page utilizes full width with 3 zone cards per row and proper spacing</t>
+          <t>Shows emissions with car equivalent comparison</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
@@ -4809,7 +4791,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Optimized Schedule</t>
+          <t>Annual Impact</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4819,28 +4801,28 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Verify Mezzanine Office Space 1 data accuracy</t>
+          <t>Verify Equipment Life Extended card</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User scrolls to Annual Impact</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>1. Locate Mezzanine Office Space 1 card
-2. Verify: Occupancy Start 07:00 AM, Optimized Start 06:18 AM, Pre-cool 45 min, End 06:00 PM, Stop 06:35 PM, Coast 15 min, Energy 0.4 kWh</t>
+          <t>1. Locate 'Equipment Life Extended' card
+2. Verify value</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Mezzanine Office Space 1 data values</t>
+          <t>Equipment Life Extended - Fewer start/stop cycles</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>All values match expected schedule and Pre-cool Duration = Occupancy Start - Optimized Start</t>
+          <t>Shows life extension benefit</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4868,49 +4850,49 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Optimized Schedule</t>
+          <t>Annual Impact</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Edge Case</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Verify handling when Optimized Stop exceeds Occupancy End</t>
+          <t>Verify Annual Impact gradient card styling</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>System calculates stop time anomaly</t>
+          <t>User scrolls to Annual Impact</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>1. Check Mezzanine Office Space 1 where Optimized Stop (06:35 PM) is AFTER Occupancy End (06:00 PM)
-2. Investigate if this is a bug or valid scenario</t>
+          <t>1. Observe 4 cards visual design
+2. Verify gradient colors</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Optimized Stop: 06:35 PM &gt; Occupancy End: 06:00 PM</t>
+          <t>Purple/green gradient cards with icons</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>This should not occur - Optimized Stop should always be before or at Occupancy End; flag as potential bug</t>
+          <t>Consistent gradient styling, proper spacing, aligned content</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Edge Case</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
@@ -4927,38 +4909,38 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Optimized Schedule</t>
+          <t>Annual Impact</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Edge Case</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Verify multiple zones can show different statuses simultaneously</t>
+          <t>Verify impact values on first day (no data)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Multiple zones are in different states</t>
+          <t>System just deployed</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>1. Observe all zone cards
-2. Verify some show 'Running — At setpoint' and others show 'Idle'</t>
+          <t>1. Navigate on day 1
+2. Check values</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Mixed statuses across zones</t>
+          <t>Day 1, no savings</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>System correctly displays different statuses per zone based on individual zone operations</t>
+          <t>Shows zero or 'Calculating...' not negative values</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -4969,7 +4951,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Edge Case</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -4986,7 +4968,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Optimized Schedule</t>
+          <t>Annual Impact</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4996,28 +4978,28 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Verify behavior with no occupancy schedule configured</t>
+          <t>Verify impact section when values show only dashes</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Zone has no occupancy schedule defined</t>
+          <t>Data unavailable</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>1. Check a zone with no schedule
-2. Observe what the card displays</t>
+          <t>1. Observe all 4 cards showing '-'
+2. Check context</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Zone with no occupancy data</t>
+          <t>All cards: '-'</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Card displays appropriate message or dashes indicating no schedule configured</t>
+          <t>Should show explanation or 'Data pending' message</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -5045,50 +5027,49 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>AI Control Mode</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Edge Case</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Verify rapid mode switching behavior</t>
+          <t>Verify footer version and copyright</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User scrolls to bottom</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>1. Quickly click between different modes multiple times
-2. Observe final state
-3. Check for errors</t>
+          <t>1. Read footer text
+2. Verify version and copyright</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Rapid clicks between Learning, Simulating, Semi-Auto, Autonomous</t>
+          <t>v1.0.0 - Test | @2026. All Right Reserved.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>System handles rapid clicks gracefully; settles on last selected mode without errors</t>
+          <t>Footer shows correct version, year, and legal text</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Edge Case</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -5105,7 +5086,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Today's Conditions</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5115,34 +5096,34 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Verify conditions update with building/location change</t>
+          <t>Verify Terms of Use link</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User at page bottom</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>1. Change building selection in 'Whitespace (DIC)' dropdown
-2. Observe if Today's Conditions update</t>
+          <t>1. Click 'Terms of Use' link
+2. Verify navigation</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Switch from Whitespace (DIC) to another building</t>
+          <t>Terms of Use link</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>All condition values update to reflect the newly selected building's weather and data</t>
+          <t>Opens Terms of Use page</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -5164,7 +5145,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Optimized Schedule</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5174,34 +5155,34 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Verify schedule changes with building selection</t>
+          <t>Verify Policy link</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>User changes building in dropdown</t>
+          <t>User at page bottom</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>1. Select a different building from header dropdown
-2. Observe schedule section update</t>
+          <t>1. Click 'Policy' link
+2. Verify navigation</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Different building selection</t>
+          <t>Policy link</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Zone cards update to show the selected building's zones and schedule data</t>
+          <t>Opens Privacy Policy page</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -5223,50 +5204,48 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Algorithm Intelligence</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Verify behavior when model has not been trained</t>
+          <t>Verify Support link</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>New building with no historical data</t>
+          <t>User at page bottom</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>1. Select a newly added building
-2. Navigate to Algorithm Intelligence section
-3. Check model accuracy fields</t>
+          <t>1. Click 'Support' link</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>New building with no training data</t>
+          <t>Support link</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Fields show 'Not yet available' or 'Training in progress' with appropriate status indicators</t>
+          <t>Opens Support/Help page or chat</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -5283,7 +5262,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Optimized Schedule</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5293,29 +5272,28 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Verify Energy Saved Today accumulates throughout the day</t>
+          <t>Verify chat widget button (bottom-right)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>User monitors page during the day</t>
+          <t>User on page</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>1. Check Energy Saved value in morning
-2. Check same zone in afternoon
-3. Compare values</t>
+          <t>1. Locate orange chat bubble bottom-right
+2. Click it</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Morning vs afternoon Energy Saved values</t>
+          <t>Chat widget button</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Energy Saved Today value increases throughout the day as optimization continues</t>
+          <t>Chat widget opens for user support</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -5353,36 +5331,34 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Verify concurrent session handling</t>
+          <t>Verify authentication required to access page</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Same user logged in on two different devices</t>
+          <t>User not logged in</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>1. Login on Device A and navigate to Start/Stop
-2. Login on Device B with same credentials
-3. Change mode on Device B
-4. Observe Device A</t>
+          <t>1. Attempt direct URL access without login
+2. Observe</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Two concurrent sessions, same user</t>
+          <t>Direct URL without session</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>System handles concurrent sessions per policy (either both update or one is invalidated)</t>
+          <t>Redirected to login; unauthorized access denied</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -5404,49 +5380,49 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Annual Impact</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Edge Case</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Verify Annual Impact with zero energy savings</t>
+          <t>Verify XSS protection in search field</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>System just started with no savings accumulated</t>
+          <t>User on page</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>1. Check Annual Impact section on day 1 of deployment
-2. Verify display with zero/minimal values</t>
+          <t>1. Enter &lt;script&gt;alert('XSS')&lt;/script&gt; in search
+2. Submit</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Annual Savings: 0, Energy Reduced: 0%</t>
+          <t>&lt;script&gt;alert('XSS')&lt;/script&gt;</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Cards show zero or 'Calculating...' without displaying negative values or errors</t>
+          <t>Input sanitized, no script execution</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Edge Case</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -5463,49 +5439,50 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Optimized Schedule</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Verify scrollability of zone cards section</t>
+          <t>Verify API endpoint security for schedule data</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>More than 12 zones configured</t>
+          <t>Dev tools open</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>1. If more zones exist than fit on screen, verify scrolling works
-2. Check if pagination exists or infinite scroll</t>
+          <t>1. Inspect network requests
+2. Verify auth tokens
+3. Replay without token</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>12+ zone cards</t>
+          <t>API request inspection</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>User can scroll/paginate through all zone cards without UI issues</t>
+          <t>APIs require valid auth; 401/403 without token</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
@@ -5522,49 +5499,50 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Optimized Schedule</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Verify time format consistency (12-hour AM/PM)</t>
+          <t>Verify session timeout handling</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User idle for extended period</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>1. Check all time values across all zone cards
-2. Verify consistent 12-hour format with AM/PM</t>
+          <t>1. Login
+2. Wait for timeout
+3. Attempt interaction</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Time format: HH:MM AM/PM</t>
+          <t>30 min idle timeout</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>All times displayed consistently in 12-hour format with AM/PM suffix</t>
+          <t>Session expires; re-login prompted</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -5581,50 +5559,50 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Today's Conditions</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Verify temperature unit consistency</t>
+          <t>Verify HTTPS enforcement for all resources</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User accesses page</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>1. Check Outdoor Temp unit
-2. Check Forecast Peak unit
-3. Verify consistency</t>
+          <t>1. Check browser security tab
+2. Verify HTTPS
+3. Check mixed content</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Temperature in °C</t>
+          <t>All resources</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>All temperature values use consistent unit (°C) throughout the page</t>
+          <t>All served over HTTPS; no mixed content</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
@@ -5641,38 +5619,38 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Algorithm Intelligence</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Verify Total Energy Saved value in Weekly Performance</t>
+          <t>Verify no sensitive data in browser console</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>User scrolls to Algorithm Intelligence section</t>
+          <t>Dev tools open</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>1. Locate Weekly Performance Summary
-2. Verify Total Energy Saved shows 1,840 kWh in green</t>
+          <t>1. Open console
+2. Check for sensitive data</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Total Energy Saved: 1,840 kWh</t>
+          <t>Console inspection</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Value is displayed in green font indicating positive savings with correct unit</t>
+          <t>No tokens, keys, passwords in console</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -5683,7 +5661,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -5700,49 +5678,50 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Verify dark/light mode toggle (if applicable)</t>
+          <t>Verify unauthorized API mode change attempt</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>Capture mode API call</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>1. Check for theme toggle in header (sun/moon icon)
-2. If present, click to switch theme</t>
+          <t>1. Capture API
+2. Replay with invalid token
+3. Observe</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Theme toggle icon</t>
+          <t>Invalid/expired token</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Page switches between light and dark mode with all elements properly styled</t>
+          <t>Server rejects with 401/403; mode unchanged</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
@@ -5759,50 +5738,49 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Optimized Schedule</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Verify behavior during daylight saving time transition</t>
+          <t>Verify SQL injection in building dropdown</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>System date is on DST transition day</t>
+          <t>Manipulate dropdown via dev tools</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>1. Set system to DST transition date
-2. Observe schedule calculations
-3. Verify no 1-hour offset errors</t>
+          <t>1. Modify dropdown to SQL payload
+2. Submit</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>DST transition: clocks spring forward/fall back</t>
+          <t>'; DROP TABLE zones; --</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Schedule correctly handles DST without duplicate or missing hours in calculations</t>
+          <t>Server rejects; no database impact</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -5829,43 +5807,1230 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Verify input validation on building/location dropdown</t>
+          <t>Verify concurrent session handling</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>User has access to dev tools</t>
+          <t>Same user, two devices</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>1. Attempt to inject SQL/script through dropdown manipulation via dev tools
-2. Modify dropdown value to malicious input
-3. Submit</t>
+          <t>1. Login Device A
+2. Login Device B
+3. Change mode on B
+4. Observe A</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>Modified dropdown value: '; DROP TABLE zones; --</t>
+          <t>Two sessions</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Server-side validation rejects malicious input; no SQL injection possible</t>
+          <t>Both sessions handled per policy; data consistent</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>TC_091</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Verify page load time under 3 seconds</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Stable network</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to page
+2. Measure full load time</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Expected: &lt; 3 seconds</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Page fully loads within 3 seconds</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>TC_092</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Verify real-time status updates</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Zones running</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>1. Observe status changes
+2. Verify auto-refresh</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Auto-refresh interval</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Status updates without full page reload</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>TC_093</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Verify page with large number of zones (50+)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Building with 50+ zones</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>1. Load page for large building
+2. Verify performance</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>50+ zones</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Renders within acceptable time; pagination if needed</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>TC_094</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Responsiveness</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Verify layout on tablet (1024x768)</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Tablet device/emulation</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>1. Open page on 1024x768
+2. Verify layout</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Tablet: 1024x768</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>2 cards per row; all content accessible</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>TC_095</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Responsiveness</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Verify layout on mobile (375x812)</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Mobile device/emulation</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>1. Open page on 375x812
+2. Verify stacking</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Mobile: 375x812</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Cards stack vertically; hamburger menu; readable</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>TC_096</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Responsiveness</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Verify layout on large monitor (2560x1440)</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Large monitor</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>1. Open on 2560x1440
+2. Verify no stretching</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>QHD: 2560x1440</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Content contained with max-width; no stretching</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>TC_097</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Optimized Schedule</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Verify behavior during daylight saving time</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>DST transition day</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>1. Set to DST date
+2. Observe schedule</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>DST spring forward/fall back</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Handles DST without missing/duplicate hours</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>TC_098</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Today's Conditions</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Verify temperature unit consistency (°C)</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>User on page</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>1. Check Outdoor Temp (°C)
+2. Check Forecast Peak (°C)</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>All in °C</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Consistent temperature unit throughout</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>TC_099</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>AI Control Mode</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Verify tooltip/info on hover for each mode</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>User hovers over modes</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>1. Hover Learning
+2. Hover Simulating
+3. Hover Semi-Auto
+4. Hover Autonomous</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Hover actions</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Tooltip explains each mode's behavior</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>TC_100</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Optimized Schedule</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Verify multiple zones show different statuses simultaneously</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Mixed states</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>1. Observe all cards
+2. Verify Running and Idle coexist</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Mixed Running/Idle</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Each zone shows independent correct status</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>TC_101</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Verify page refresh maintains current state</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>User on page, Semi-Auto selected</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>1. Press F5
+2. Verify mode and data persist</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Page refresh</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Maintains AI mode selection and latest data</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>TC_102</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Verify search with empty input</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>User on page</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>1. Click search
+2. Press Enter without typing</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Empty search</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>No error; shows all or no action</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>TC_103</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Verify search with special characters</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>User on page</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>1. Type !@#$%^&amp;*() in search
+2. Submit</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>!@#$%^&amp;*()</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Handled gracefully; no error/crash</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>TC_104</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Optimized Schedule</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Verify Pre-cool 78 min calculation (Mezzanine Pantry)</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Schedule loaded</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>1. Pantry: 08:00 AM - 06:42 AM = 78 min
+2. Verify displayed value</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>08:00 - 06:42 = 78 min</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Pre-cool correctly shows 78 min</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>TC_105</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Optimized Schedule</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Verify zone card hover/click interaction</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>User views zone cards</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>1. Hover over card
+2. Click card
+3. Observe</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Zone card interaction</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Card shows hover effect; may open detail view</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>TC_106</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Optimized Schedule</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Verify data refresh interval for zone cards</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>System running</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>1. Note Energy Saved
+2. Wait
+3. Check update</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Auto-refresh</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Data refreshes at regular intervals</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>TC_107</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Today's Conditions</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Verify display when humidity is 0% or 100%</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Extreme humidity data</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>1. System receives 0% or 100% humidity
+2. Observe display</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Humidity: 0% or 100%</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Displays correctly without UI issues</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>TC_108</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>AI Control Mode</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Verify mode switch with network disconnection mid-switch</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>User switches mode, network drops</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>1. Start mode switch
+2. Disconnect network mid-request
+3. Observe</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Network failure during API call</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Shows error with retry; stays on previous mode</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>TC_109</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Optimized Schedule</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Verify zone card when zone goes offline</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Zone sensor/controller offline</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>1. Simulate zone going offline
+2. Observe card status</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Zone offline event</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Card shows 'Offline' or 'Communication Error' status</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>TC_110</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Verify CSRF token on mode change API</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>User with dev tools</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>1. Inspect mode change POST request
+2. Check for CSRF token
+3. Replay without token</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>CSRF token validation</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Request rejected without valid CSRF token</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="K91" s="2" t="inlineStr">
+      <c r="K111" s="2" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="L91" s="2" t="inlineStr">
+      <c r="L111" s="2" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
@@ -5882,22 +7047,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="58" customWidth="1" min="8" max="8"/>
+    <col width="68" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5985,34 +7150,33 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Optimized Stop time exceeds Occupancy End for Mezzanine Office Space 1</t>
+          <t>Optimized Stop exceeds Occupancy End - Mezzanine Office Space 1</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page with schedule loaded</t>
+          <t>User on Start/Stop page</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Start/Stop page
-2. Locate Mezzanine Office Space 1 card
-3. Compare Optimized Stop (06:35 PM) with Occupancy End (06:00 PM)</t>
+          <t>1. Locate Mezzanine Office Space 1
+2. Compare Stop (06:35 PM) with End (06:00 PM)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Optimized Stop: 06:35 PM, Occupancy End: 06:00 PM</t>
+          <t>Stop: 06:35 PM, End: 06:00 PM</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Optimized Stop should be BEFORE Occupancy End to allow coast-through period (HVAC stops early, building coasts on stored energy)</t>
+          <t>Optimized Stop should be BEFORE Occupancy End for coast-through savings</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Optimized Stop (06:35 PM) is 35 minutes AFTER Occupancy End (06:00 PM), contradicting the coast-through optimization logic</t>
+          <t>Optimized Stop is 35 min AFTER Occupancy End, violating coast-through logic</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -6054,44 +7218,43 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Mezzanine Office Space 2 Optimized Stop exceeds Occupancy End</t>
+          <t>Optimized Stop exceeds Occupancy End - Mezzanine Pantry</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User on Start/Stop page</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Start/Stop page
-2. Locate Mezzanine Office Space 2 card
-3. Compare Optimized Stop (05:35 PM) with Occupancy End (06:00 PM)</t>
+          <t>1. Locate Mezzanine Pantry
+2. Compare Stop (06:22 PM) with End (06:00 PM)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Optimized Stop: 05:35 PM, Occupancy End: 06:00 PM</t>
+          <t>Stop: 06:22 PM, End: 06:00 PM</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Optimized Stop should be before Occupancy End with a positive coast duration</t>
+          <t>Optimized Stop should be before Occupancy End</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Coast Duration shows '25 min saved' but the time difference is only 25 min (06:00 PM - 05:35 PM = 25 min). While this specific case appears correct, it's inconsistent with similar zones showing different patterns</t>
+          <t>Optimized Stop is 22 min AFTER Occupancy End</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -6118,49 +7281,48 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Inconsistent zone naming convention - White_Space-Corridor uses underscore and hyphen</t>
+          <t>Optimized Stop exceeds Occupancy End - White Space 01</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User on Start/Stop page</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1. Observe all zone card names
-2. Note 'White_Space-Corridor' uses underscore and hyphen
-3. Compare with 'White Space 01', 'White Space 02'</t>
+          <t>1. Locate White Space 01
+2. Compare Stop (06:22 PM) with End (06:00 PM)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Zone names: White Space 01, White Space 02, White_Space-Corridor</t>
+          <t>Stop: 06:22 PM, End: 06:00 PM</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Consistent naming convention across all zones (either spaces, underscores, or hyphens - not mixed)</t>
+          <t>Optimized Stop should be before Occupancy End</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>White_Space-Corridor uses mixed separators (underscore and hyphen) while other White Space zones use spaces</t>
+          <t>Optimized Stop is 22 min AFTER Occupancy End</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -6192,44 +7354,43 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>White_Space-Corridor shows all dashes with no explanation</t>
+          <t>Optimized Stop exceeds Occupancy End - Office 01 (largest discrepancy)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User on Start/Stop page</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1. Locate White_Space-Corridor card
-2. Observe all fields show '-' (dash)
-3. No tooltip or explanation provided</t>
+          <t>1. Locate Office 01
+2. Compare Stop (06:40 PM) with End (06:00 PM)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>All fields: '-'</t>
+          <t>Stop: 06:40 PM, End: 06:00 PM</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>If zone has no schedule, show a clear message like 'No schedule configured' or 'Unoccupied zone' instead of just dashes</t>
+          <t>Optimized Stop should be before Occupancy End</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Zone card displays only dashes without any context or explanation for why data is unavailable</t>
+          <t>Optimized Stop is 40 min AFTER Occupancy End - LARGEST discrepancy</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6251,54 +7412,53 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Today's Conditions</t>
+          <t>Optimized Schedule</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Temperature Compliance shows 8% but marked as 'Normal weekday'</t>
+          <t>Optimized Stop exceeds Occupancy End - Mezzanine Office Space 3</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User on Start/Stop page</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1. Locate Temperature Compliance card
-2. Note value shows '8%'
-3. Subtitle says 'Normal weekday'</t>
+          <t>1. Locate Mezz Office Space 3
+2. Compare Stop (06:30 PM) with End (06:00 PM)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Temperature Compliance: 8%, Normal weekday</t>
+          <t>Stop: 06:30 PM, End: 06:00 PM</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8% compliance seems very low for 'Normal weekday' - should either show higher compliance or label should indicate an issue</t>
+          <t>Optimized Stop should be before Occupancy End</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8% Temperature Compliance is displayed with green indicator and 'Normal weekday' label, which is confusing - unclear if 8% means 8% non-compliant or 8% of target achieved</t>
+          <t>Optimized Stop is 30 min AFTER Occupancy End</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -6330,33 +7490,33 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Mezzanine Pantry Optimized Stop (06:22 PM) exceeds Occupancy End (06:00 PM)</t>
+          <t>Coast Duration shows 'saved' when system runs past occupancy end</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>Zones where Stop &gt; End</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1. Locate Mezzanine Pantry card
-2. Compare Occupancy End (06:00 PM) and Optimized Stop (06:22 PM)</t>
+          <t>1. Observe zones with Stop &gt; End
+2. Note Coast Duration still says 'XX min saved'</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Occupancy End: 06:00 PM, Optimized Stop: 06:22 PM</t>
+          <t>Coast Duration: 15 min saved (Mezz Space 1)</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Optimized Stop should be before Occupancy End for coast-through savings</t>
+          <t>Should not say 'saved' when running overtime (wastes energy)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Optimized Stop (06:22 PM) is 22 minutes AFTER Occupancy End (06:00 PM), defying the coast-through optimization purpose</t>
+          <t>Displays 'min saved' even when running PAST occupancy end - misleading</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6398,43 +7558,44 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>White Space 01 Optimized Stop (06:22 PM) exceeds Occupancy End (06:00 PM)</t>
+          <t>Pre-cool Duration calculation error - White Space 03</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User on Start/Stop page</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1. Locate White Space 01 card
-2. Compare Occupancy End (06:00 PM) and Optimized Stop (06:22 PM)</t>
+          <t>1. White Space 03: Occupancy 07:00 AM, Optimized 06:55 AM
+2. 07:00 - 06:55 = 5 min
+3. Displayed: 65 min</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Occupancy End: 06:00 PM, Optimized Stop: 06:22 PM</t>
+          <t>Start 07:00, Optimized 06:55, Shown: 65 min</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Optimized Stop should be before Occupancy End</t>
+          <t>Pre-cool should be 5 min (07:00 AM - 06:55 AM)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Optimized Stop is 22 minutes AFTER Occupancy End, same issue as other zones</t>
+          <t>Shows 65 min instead of 5 min - major calculation error or wrong Optimized Start displayed</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -6461,48 +7622,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Office 01 Optimized Stop (06:40 PM) exceeds Occupancy End (06:00 PM)</t>
+          <t>Inconsistent zone naming - White_Space-Corridor uses mixed separators</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User on Start/Stop page</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1. Locate Office 01 card
-2. Compare Occupancy End (06:00 PM) and Optimized Stop (06:40 PM)</t>
+          <t>1. Observe names: 'White Space 01/02/03' vs 'White_Space-Corridor'</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Occupancy End: 06:00 PM, Optimized Stop: 06:40 PM</t>
+          <t>White Space 01 vs White_Space-Corridor</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Optimized Stop should be before Occupancy End</t>
+          <t>Consistent naming convention (all spaces OR underscores)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Optimized Stop is 40 minutes AFTER Occupancy End - the largest discrepancy among all zones</t>
+          <t>Mixed separators: spaces in some, underscore+hyphen in corridor</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -6529,40 +7689,39 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>UI/UX</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>White Space 03 Optimized Stop (05:40 PM) shows inconsistency with Coast Duration</t>
+          <t>White_Space-Corridor shows only dashes with no context</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User on Start/Stop page</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1. Locate White Space 03 card
-2. Occupancy End: 06:00 PM, Optimized Stop: 05:40 PM
-3. Coast Duration: 20 min saved
-4. Verify: 06:00 PM - 05:40 PM = 20 min ✓</t>
+          <t>1. Locate White_Space-Corridor
+2. All fields show '-'
+3. No tooltip/explanation</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Occupancy End: 06:00 PM, Optimized Stop: 05:40 PM, Coast: 20 min</t>
+          <t>All fields: '-'</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>This zone is correct, but inconsistency with other zones having Stop &gt; End raises data integrity concerns</t>
+          <t>Should show 'No schedule configured' or explanatory tooltip</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Some zones correctly show Optimized Stop before Occupancy End while others show it after - indicates systematic calculation bug affecting specific zones</t>
+          <t>Only dashes without any contextual information or status</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6572,7 +7731,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -6594,7 +7753,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Optimized Schedule</t>
+          <t>Today's Conditions</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -6604,43 +7763,44 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Coast Duration label says 'saved' which is misleading when Stop exceeds End</t>
+          <t>Temperature Compliance 8% with 'Normal weekday' is ambiguous</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User on Start/Stop page</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1. Observe zones where Optimized Stop &gt; Occupancy End
-2. Note Coast Duration still shows 'XX min saved'</t>
+          <t>1. Temperature Compliance: 8%
+2. Green indicator
+3. 'Normal weekday' subtitle</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Coast Duration: 15 min saved (Mezzanine Office Space 1)</t>
+          <t>8%, green, Normal weekday</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>If Optimized Stop is AFTER Occupancy End, there is no coast savings - the label 'saved' is incorrect</t>
+          <t>Should clarify: is 8% the violation rate (good) or compliance rate (bad)?</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Coast Duration shows 'min saved' even when the system is running PAST occupancy end, which is energy waste not savings</t>
+          <t>8% with green and 'Normal' is confusing - metric meaning unclear</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -6672,7 +7832,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Copyright text shows '@2026' instead of '©2026'</t>
+          <t>Copyright shows '@' instead of '©' symbol</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -6682,24 +7842,22 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1. Scroll to page footer
-2. Observe copyright text
-3. Note '@' symbol used instead of '©'</t>
+          <t>1. Read footer: '@2026' instead of '©2026'</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Footer text: v1.0.0 - Test | @2026. All Right Reserved.</t>
+          <t>@2026</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Copyright symbol should be '©' (©2026) and 'All Rights Reserved' (plural 'Rights')</t>
+          <t>Should use proper copyright symbol: ©2026</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Footer shows '@2026' instead of '©2026' and 'All Right Reserved' instead of 'All Rights Reserved'</t>
+          <t>Uses '@2026' instead of '©2026'</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6731,7 +7889,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Annual Impact</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -6741,43 +7899,42 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Annual Impact values show '-' (no data) despite system being operational</t>
+          <t>Grammar: 'All Right Reserved' should be 'All Rights Reserved'</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>System is operational with schedule running</t>
+          <t>User scrolls to footer</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1. Scroll to Annual Impact section
-2. Observe all four cards show '-' as values</t>
+          <t>1. Read 'All Right Reserved' in footer</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>All Annual Impact metrics showing '-'</t>
+          <t>All Right Reserved</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Annual Impact cards should show accumulated values or 'Calculating' status for operational systems</t>
+          <t>Should be 'All Rights Reserved' (plural)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>All four Annual Impact cards (Savings, Energy Reduced, Emissions, Equipment Life) display only '-' with no context</t>
+          <t>Missing 's' - grammatically incorrect</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -6799,44 +7956,43 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Algorithm Intelligence</t>
+          <t>Annual Impact</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Algorithm Intelligence parameters all show '-' (no expandable data)</t>
+          <t>All Annual Impact cards show only '-' with no explanation</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User scrolls to Annual Impact</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1. Scroll to Algorithm Intelligence section
-2. Check all parameter fields
-3. Most show only '-' or expand arrow with no visible data</t>
+          <t>1. Observe all 4 cards showing '-'
+2. No context provided</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Parameters showing '-' with expand arrows</t>
+          <t>All values: '-'</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Parameters should show current values or 'N/A - Learning mode' if not yet available</t>
+          <t>Should show values or 'Requires 30 days data' explanation</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>All expandable parameters across all Algorithm Intelligence cards show only dashes with no actionable information</t>
+          <t>Only dashes with no user guidance on why data unavailable</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6868,7 +8024,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Optimized Schedule</t>
+          <t>Algorithm Intelligence</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -6878,45 +8034,43 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Office 02 Optimized Stop (05:22 PM) shows Coast Duration as 38 min but actual difference is 38 min</t>
+          <t>All Algorithm Intelligence parameters show '-' (no data)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>User is on Start/Stop page</t>
+          <t>User in Algorithm Intelligence section</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1. Locate Office 02 card
-2. Occupancy End: 06:00 PM, Optimized Stop: 05:22 PM
-3. Calculate: 06:00 PM - 05:22 PM = 38 min
-4. Coast Duration shows: 38 min saved ✓</t>
+          <t>1. Check all expandable parameters
+2. All show '-'</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Office 02: End 06:00 PM, Stop 05:22 PM, Coast 38 min</t>
+          <t>All params: '-'</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Calculation is correct for this zone, confirming the logic should have Stop &lt; End everywhere</t>
+          <t>Should show values or 'Learning in progress' status</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>This zone is correct - further confirms that zones with Stop &gt; End are bugs, not features</t>
+          <t>All parameters show dashes with no actionable information</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -6943,56 +8097,262 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Mezzanine Office Space 2 shows 'Idle' during occupancy hours</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>User on page during business hours (after 07:00 AM)</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1. Mezz Space 2: Occupancy Start 07:00 AM
+2. Current time past 07:00 AM
+3. Status shows 'Idle'</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Status: Idle during occupied hours</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Zone should be 'Running' during occupancy hours or show fault status</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Shows 'Idle' when zone should be actively conditioning for occupants</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Web - Chrome/Desktop</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>BUG_016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Optimized Schedule</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Electrical Room has occupancy-based optimization (unusual for utility space)</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>User on Start/Stop page</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1. Locate Electrical Room
+2. Has full occupancy schedule like offices</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Electrical Room with occupancy times</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Utility spaces typically need equipment-based scheduling, not occupancy-based</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Treated as occupied space with pre-cool/coast which is unusual for electrical rooms</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Web - Chrome/Desktop</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>BUG_017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Today's Conditions</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
           <t>UI/UX</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Electrical Room shows Occupancy Start 07:00 AM but some other cards show 08:00 AM without clear explanation</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>User is on Start/Stop page</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1. Compare Occupancy Start times across zone cards
-2. Note Electrical Room: 07:00 AM vs Office 02: 08:00 AM</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Different Occupancy Start times across zones</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Different start times are acceptable if configured per zone, but there should be a way to verify/configure them</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>Not a confirmed bug - different zones may have different occupancy schedules. However, an Electrical Room having early occupancy (07:00 AM) seems unusual for a utility space</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>'No of Rooms: 12' subtitle 'Building retained heat' is confusing</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>User on Start/Stop page</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1. No of Rooms card: 12
+2. Subtitle: 'Building retained heat'</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>12, Building retained heat</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Subtitle should explain the number (e.g., '12 zones optimized today')</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>'Building retained heat' doesn't explain what the 12 rooms represent</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Web - Chrome/Desktop</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>BUG_018</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Optimized Schedule</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Multiple zones with excessively long Pre-cool Duration (78 min)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>User on Start/Stop page</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1. Mezzanine Pantry: 78 min pre-cool
+2. Office 02: 78 min pre-cool
+3. Compare with typical 45-55 min</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>78 min vs typical 45-55 min</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>78 min pre-cool may indicate algorithm tuning issue or oversized zones needing investigation</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Two zones require 78 min pre-cooling which is 40-70% longer than average zones - potential inefficiency</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>Web - Chrome/Desktop</t>
         </is>
